--- a/esempioReale_corretto.xlsx
+++ b/esempioReale_corretto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Piazza Condini, Romagnano, Trento, Italy</t>
+          <t>Piazza Condini, 38123 Romagnano, Trento, TN, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Via del Comun, 8, Commezzadura, Trento, Italy</t>
+          <t>Via del Comun, 8, 38020 Commezzadura, TN, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -489,7 +489,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viale De Gasperi, 69, Avio, Trento, Italy</t>
+          <t>Viale Alcide Degasperi, 69, 38063 Avio, TN, Italia</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Via 24 Maggio, 115, Lodrone, Trento, Italy</t>
+          <t>Via 24 Maggio, 115, 38089 Lodrone, Storo, TN, Italia</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -527,7 +527,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strada Provinciale di Seregnano, 4, Civezzano, Trento, Italy</t>
+          <t>Frazione Cogatti, 4, 38045 Seregnano, Civezzano, TN, Italia</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -546,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Piazza Fiera, Cles, Trento, Italy</t>
+          <t>Piazza Fiera, 38023 Cles, TN, Italia</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Balbido, 1, 38071, Bleggio Superiore, Trento, Italy</t>
+          <t>Frazione Balbido, 1, 38071 Bleggio Superiore, TN, Italia</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -584,7 +584,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Via Biasi, 1, 38010, San Michele all'Adige, Trento, Italy</t>
+          <t>Via Biasi, 1, 38010 San Michele all'Adige, TN, Italia</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Piazzale Stazione, Mezzolombardo, Trento, Italy</t>
+          <t>Mezzolombardo Stazione FTM, 38017 Mezzolombardo, TN, Italia</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Via Spiazzi, 2, Zivignago, Trento, Italy</t>
+          <t>Via Spiazzi, 2, 38057 Canezza, Pergine Valsugana, TN, Italia</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corso De Gasperi, 8, Predazzo, Trento, Italy</t>
+          <t>Corso Degasperi, 8, 38037 Predazzo, TN, Italia</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -660,7 +660,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via Sant'Alessandro, 11, Riva del Garda, Trento, Italy</t>
+          <t>Via S. Alessandro, 11, 38066 Riva del Garda, TN, Italia</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Via dei Laghi, 47, 38060, Tenno, Trento, Italy</t>
+          <t>Via dei Laghi, 47, 38060 Tenno, TN, Italia</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viale Trento, Rovereto, Trento, Italy</t>
+          <t>Viale Trento, 38068 Rovereto, TN, Italia</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Via Roma, Ospedaletto, Trento, Italy</t>
+          <t>Via Roma, 38050 Ospedaletto, TN, Italia</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -744,7 +744,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Via Alcide De Gasperi, 5, 38096, Terlago, Trento, Italy</t>
+          <t>Via Alcide De Gasperi, 5, 38096 Terlago, TN, Italia</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -763,7 +763,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Piazza de Ciampiedel, Campitello di Fassa, Trento, Italy</t>
+          <t>Piazza Gries, 38032 Canazei, TN, Italia</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -782,7 +782,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Via Temanza, Borgo Valsugana, Trento, Italy</t>
+          <t>Via Temanza, 38051 Borgo Valsugana, TN, Italia</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Piazza de Ciampiedel, Campitello di Fassa, Trento, Italy</t>
+          <t>Piazza San Filippo e Giacomo, 38031 Campitello di Fassa, TN, Italia</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Via Albere, 2, Tenna, Trento, Italy</t>
+          <t>Via Alberè, 2, 38050 Tenna, TN, Italia</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Via della Credenza, Taio, Trento, Italy</t>
+          <t>Via Degli Alpini, 38012 Taio, Predaia, TN, Italia</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -853,36 +853,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Trento 7</t>
+          <t>Rovereto 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trento, Trento, Italy</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>23</v>
-      </c>
+          <t>Via Alessandro Manzoni, 3, 38068 Rovereto, TN, Italia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Rovereto 2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Via Alessandro Manzoni, 3, 38068, Rovereto, Trento, Italy</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="b">
         <v>1</v>
       </c>
     </row>

--- a/esempioReale_corretto.xlsx
+++ b/esempioReale_corretto.xlsx
@@ -1,34 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dev/Desktop/busplan/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F46F1E5-CB2C-AA43-9A12-66924407833F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="16600" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Indirizzo</t>
+  </si>
+  <si>
+    <t>Partecipanti</t>
+  </si>
+  <si>
+    <t>Istituto</t>
+  </si>
+  <si>
+    <t>AI_Corrected</t>
+  </si>
+  <si>
+    <t>IC Aldeno-Mattarello</t>
+  </si>
+  <si>
+    <t>Piazza Condini, Romagnano, 38123 Trento TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Alta Val di Sole</t>
+  </si>
+  <si>
+    <t>Via del Comun, 8, 38020 Commezzadura TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Avio</t>
+  </si>
+  <si>
+    <t>Viale Alcide Degasperi, 69, 38063 Avio TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Chiese</t>
+  </si>
+  <si>
+    <t>Via 24 Maggio, 115, Lodrone, 38083 Storo TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Civezzano</t>
+  </si>
+  <si>
+    <t>Frazione Cogatti, 4, Seregnano, 38045 Civezzano TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Cles</t>
+  </si>
+  <si>
+    <t>Piazza Fiera, 38023 Cles TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Giudicarie Esteriori</t>
+  </si>
+  <si>
+    <t>Località Balbido, 1, 38071 Bleggio Superiore TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Mezzocorona</t>
+  </si>
+  <si>
+    <t>Via Biasi, 1, 38010 San Michele all'Adige TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Mezzolombardo-Paganella</t>
+  </si>
+  <si>
+    <t>Mezzolombardo Stazione FTM, 38017 Mezzolombardo TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Pergine 1</t>
+  </si>
+  <si>
+    <t>Via Spiazzi, 2, 38057 Pergine Valsugana TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Predazzo-Tesero</t>
+  </si>
+  <si>
+    <t>Corso de Gasperi, 8, 38037 Predazzo TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Riva 1</t>
+  </si>
+  <si>
+    <t>Via S.Alessandro, 11, 38066 Riva del Garda TN, Italia</t>
+  </si>
+  <si>
+    <t>Riva</t>
+  </si>
+  <si>
+    <t>IC Riva 2</t>
+  </si>
+  <si>
+    <t>Via dei Laghi, 47, 38060 Tenno TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Rovereto Nord</t>
+  </si>
+  <si>
+    <t>Viale Trento, 38068 Rovereto TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Strigno-Tesino</t>
+  </si>
+  <si>
+    <t>Via Roma, 38050 Ospedaletto TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Vezzano</t>
+  </si>
+  <si>
+    <t>Via Alcide Degasperi, 5, Terlago, 38096 Vallelaghi TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Ladino di Fassa</t>
+  </si>
+  <si>
+    <t>Piazza Gries, 38032 Canazei TN, Italia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC borgo Valsugana </t>
+  </si>
+  <si>
+    <t>Via Temanza, 38051 Borgo Valsugana TN, Italia</t>
+  </si>
+  <si>
+    <t>IC LADINO DI FASSA</t>
+  </si>
+  <si>
+    <t>Piaz de Ciampedel, 38031 Campitello di Fassa TN, Italia</t>
+  </si>
+  <si>
+    <t>IC Levico terme</t>
+  </si>
+  <si>
+    <t>Via Alberè, 2, 38050 Tenna TN, Italia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC Taio </t>
+  </si>
+  <si>
+    <t>Taio, 38012 Predaia TN, Italia</t>
+  </si>
+  <si>
+    <t>Rovereto 2</t>
+  </si>
+  <si>
+    <t>Via Alessandro Manzoni, 3, 38068 Rovereto TN, Italia</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +206,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,461 +508,338 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="45.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Indirizzo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Partecipanti</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Istituto</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>AI_Corrected</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>IC Aldeno-Mattarello</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Piazza Condini, 38123 Romagnano, Trento, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
         <v>14</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>IC Alta Val di Sole</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Via del Comun, 8, 38020 Commezzadura, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>13</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IC Avio</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Viale Alcide Degasperi, 69, 38063 Avio, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
         <v>28</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IC Chiese</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Via 24 Maggio, 115, 38089 Lodrone, Storo, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
         <v>14</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IC Civezzano</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Frazione Cogatti, 4, 38045 Seregnano, Civezzano, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>IC Cles</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Piazza Fiera, 38023 Cles, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
         <v>20</v>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IC Giudicarie Esteriori</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Frazione Balbido, 1, 38071 Bleggio Superiore, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
         <v>14</v>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IC Mezzocorona</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Via Biasi, 1, 38010 San Michele all'Adige, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
         <v>17</v>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IC Mezzolombardo-Paganella</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mezzolombardo Stazione FTM, 38017 Mezzolombardo, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10">
         <v>23</v>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IC Pergine 1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Via Spiazzi, 2, 38057 Canezza, Pergine Valsugana, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11">
+        <v>24</v>
+      </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IC Predazzo-Tesero</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Corso Degasperi, 8, 38037 Predazzo, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
         <v>20</v>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IC Riva 1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Via S. Alessandro, 11, 38066 Riva del Garda, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13">
         <v>22</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Riva</t>
-        </is>
+      <c r="D13" t="s">
+        <v>29</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IC Riva 2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Via dei Laghi, 47, 38060 Tenno, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14">
         <v>15</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Riva</t>
-        </is>
+      <c r="D14" t="s">
+        <v>29</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IC Rovereto Nord</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viale Trento, 38068 Rovereto, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15">
         <v>25</v>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>IC Strigno-Tesino</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Via Roma, 38050 Ospedaletto, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16">
         <v>26</v>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IC Vezzano</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Via Alcide De Gasperi, 5, 38096 Terlago, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IC Ladino di Fassa</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Piazza Gries, 38032 Canazei, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18">
         <v>26</v>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IC borgo Valsugana </t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Via Temanza, 38051 Borgo Valsugana, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19">
         <v>21</v>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IC LADINO DI FASSA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Piazza San Filippo e Giacomo, 38031 Campitello di Fassa, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20">
         <v>27</v>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IC Levico terme</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Via Alberè, 2, 38050 Tenna, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21">
         <v>17</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IC Taio </t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Via Degli Alpini, 38012 Taio, Predaia, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22">
         <v>23</v>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Rovereto 2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Via Alessandro Manzoni, 3, 38068 Rovereto, TN, Italia</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
